--- a/results/tables/master_table_all_checkpoints.xlsx
+++ b/results/tables/master_table_all_checkpoints.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kgaer\code\RL_GSPO_Qwen2.5VLM\results\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83082847-1890-4BE1-BC45-A18147AE5E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6599BCE4-9AF9-4BA5-B701-360D07DF5A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" tabRatio="560" xr2:uid="{A5579D8F-B6C5-43E4-8CB2-6BF5F062D88C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" tabRatio="560" activeTab="1" xr2:uid="{A5579D8F-B6C5-43E4-8CB2-6BF5F062D88C}"/>
   </bookViews>
   <sheets>
     <sheet name="master_table_all_checkpoints" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="452">
   <si>
     <t>Milestone ID</t>
   </si>
@@ -1325,13 +1326,209 @@
   </si>
   <si>
     <t>/tmp/rl-gspo-qwen2-5vlm-phase-d-final/RL_GSPO_Qwen2.5VLM/outputs_staged_phase_d_from_large_phase_c/phase_d/checkpoint-130/summary.txt</t>
+  </si>
+  <si>
+    <t>Kaggle notebook title</t>
+  </si>
+  <si>
+    <t>Repo notebook file</t>
+  </si>
+  <si>
+    <t>Attached datasets</t>
+  </si>
+  <si>
+    <t>Output root</t>
+  </si>
+  <si>
+    <t>Produced checkpoints</t>
+  </si>
+  <si>
+    <t>RL GSPO Qwen2.5VLM Staged Train</t>
+  </si>
+  <si>
+    <t>kaggle_staged_train.ipynb</t>
+  </si>
+  <si>
+    <t>RL GSPO Qwen2.5VLM Staged Code</t>
+  </si>
+  <si>
+    <r>
+      <t>A: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>49</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>; B: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>60,120,180,240,242</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>; C: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>60,119</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>; D: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>30</t>
+    </r>
+  </si>
+  <si>
+    <t>RL GSPO Qwen2.5VLM Large Split Continue</t>
+  </si>
+  <si>
+    <t>kaggle_staged_train_large_continue.ipynb</t>
+  </si>
+  <si>
+    <r>
+      <t>RL GSPO Qwen2.5VLM Staged Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RL GSPO Qwen2.5-VLM PhaseC Best Checkpoint</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>60,120,180,240,300,360,420,480,540,600,602</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>; D: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>60,120,130</t>
+    </r>
+  </si>
+  <si>
+    <t>RL GSPO Qwen2.5VLM Phase D Large Continue</t>
+  </si>
+  <si>
+    <t>kaggle_staged_train_phase_d_from_large_continue.ipynb</t>
+  </si>
+  <si>
+    <r>
+      <t>RL GSPO Qwen2.5VLM Staged Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RL GSPO Qwen2.5-VLM Large PhaseC Best Checkpoint</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>60,120,130</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1465,6 +1662,24 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1820,10 +2035,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1869,7 +2093,141 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1999,6 +2357,26 @@
     <tableColumn id="102" xr3:uid="{D38AB055-BE91-4036-BDDE-B4DF824C903F}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB12D11F-6CDE-43D8-B503-2299EBB82116}" name="Table2" displayName="Table2" ref="A1:E4" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:E4" xr:uid="{CB12D11F-6CDE-43D8-B503-2299EBB82116}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{3A1A628A-291A-4B6E-8AD5-A5E7B68BC13C}" name="Kaggle notebook title" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{8E6E87BD-641C-4653-83DD-9055C7E98922}" name="Repo notebook file" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{E5237356-F5A5-4031-857D-FC529BC43159}" name="Attached datasets" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{A41D81C4-33AB-4172-8E87-1DA8FB2281EB}" name="Output root" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{5290B8EB-CA2B-4B4E-8701-9E287D3D6751}" name="Produced checkpoints" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3460,7 +3838,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>123</v>
       </c>
@@ -3747,7 +4125,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>123</v>
       </c>
@@ -4034,7 +4412,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>123</v>
       </c>
@@ -4321,7 +4699,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>123</v>
       </c>
@@ -6067,7 +6445,7 @@
       </c>
       <c r="CX13" s="2"/>
     </row>
-    <row r="14" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>264</v>
       </c>
@@ -6354,7 +6732,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="15" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>264</v>
       </c>
@@ -6641,7 +7019,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="16" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:102" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>264</v>
       </c>
@@ -6928,7 +7306,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="17" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>264</v>
       </c>
@@ -7215,7 +7593,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="18" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>264</v>
       </c>
@@ -7502,7 +7880,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="19" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>264</v>
       </c>
@@ -7789,7 +8167,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>264</v>
       </c>
@@ -8076,7 +8454,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="21" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>264</v>
       </c>
@@ -8363,7 +8741,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="22" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>264</v>
       </c>
@@ -8943,7 +9321,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>264</v>
       </c>
@@ -9230,7 +9608,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="25" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>264</v>
       </c>
@@ -9810,7 +10188,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="27" spans="2:101" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:101" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>403</v>
       </c>
@@ -10393,4 +10771,93 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08AE19F-F136-4CCA-8A4B-31AF8F8322E5}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/results/tables/master_table_all_checkpoints.xlsx
+++ b/results/tables/master_table_all_checkpoints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kgaer\code\RL_GSPO_Qwen2.5VLM\results\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6599BCE4-9AF9-4BA5-B701-360D07DF5A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267C9F89-272D-4B71-AD87-77C2B17A8468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" tabRatio="560" activeTab="1" xr2:uid="{A5579D8F-B6C5-43E4-8CB2-6BF5F062D88C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" tabRatio="560" xr2:uid="{A5579D8F-B6C5-43E4-8CB2-6BF5F062D88C}"/>
   </bookViews>
   <sheets>
     <sheet name="master_table_all_checkpoints" sheetId="1" r:id="rId1"/>
@@ -2111,7 +2111,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2128,25 +2128,6 @@
         <color theme="1"/>
         <name val="Consolas"/>
         <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2226,6 +2207,25 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2361,7 +2361,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB12D11F-6CDE-43D8-B503-2299EBB82116}" name="Table2" displayName="Table2" ref="A1:E4" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB12D11F-6CDE-43D8-B503-2299EBB82116}" name="Table2" displayName="Table2" ref="A1:E4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E4" xr:uid="{CB12D11F-6CDE-43D8-B503-2299EBB82116}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2370,11 +2370,11 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3A1A628A-291A-4B6E-8AD5-A5E7B68BC13C}" name="Kaggle notebook title" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{8E6E87BD-641C-4653-83DD-9055C7E98922}" name="Repo notebook file" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{E5237356-F5A5-4031-857D-FC529BC43159}" name="Attached datasets" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{A41D81C4-33AB-4172-8E87-1DA8FB2281EB}" name="Output root" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5290B8EB-CA2B-4B4E-8701-9E287D3D6751}" name="Produced checkpoints" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3A1A628A-291A-4B6E-8AD5-A5E7B68BC13C}" name="Kaggle notebook title" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{8E6E87BD-641C-4653-83DD-9055C7E98922}" name="Repo notebook file" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{E5237356-F5A5-4031-857D-FC529BC43159}" name="Attached datasets" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{A41D81C4-33AB-4172-8E87-1DA8FB2281EB}" name="Output root" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{5290B8EB-CA2B-4B4E-8701-9E287D3D6751}" name="Produced checkpoints" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
